--- a/research/traditional_assets/database/data/bulgaria/bulgaria_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_financial_svcs_non_bank_insurance.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.308</v>
+        <v>0.129</v>
       </c>
       <c r="E2">
-        <v>0.129</v>
+        <v>0.185</v>
       </c>
       <c r="G2">
-        <v>0.1878172588832487</v>
+        <v>0.2853519340519975</v>
       </c>
       <c r="H2">
-        <v>0.1878172588832487</v>
+        <v>0.2853519340519975</v>
       </c>
       <c r="I2">
-        <v>0.2098138747884941</v>
+        <v>0.2415979708306912</v>
       </c>
       <c r="J2">
-        <v>0.1877437433683499</v>
+        <v>0.2165040893320149</v>
       </c>
       <c r="K2">
-        <v>5.931</v>
+        <v>6.02</v>
       </c>
       <c r="L2">
-        <v>0.3345177664974619</v>
+        <v>0.3817374762206722</v>
       </c>
       <c r="M2">
-        <v>3.6178</v>
+        <v>3.59</v>
       </c>
       <c r="N2">
-        <v>0.05320294117647058</v>
+        <v>0.05472560975609756</v>
       </c>
       <c r="O2">
-        <v>0.6099814533805429</v>
+        <v>0.5963455149501661</v>
       </c>
       <c r="P2">
-        <v>2.2628</v>
+        <v>3.59</v>
       </c>
       <c r="Q2">
-        <v>0.0332764705882353</v>
+        <v>0.05472560975609756</v>
       </c>
       <c r="R2">
-        <v>0.3815208227954813</v>
+        <v>0.5963455149501661</v>
       </c>
       <c r="S2">
-        <v>1.355</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.3745370114434187</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>93.182</v>
+        <v>104.782</v>
       </c>
       <c r="V2">
-        <v>1.370323529411765</v>
+        <v>1.597286585365854</v>
       </c>
       <c r="W2">
-        <v>0.1418897637795276</v>
+        <v>0.2030864197530864</v>
       </c>
       <c r="X2">
-        <v>0.02618954535682164</v>
+        <v>0.0531669950359083</v>
       </c>
       <c r="Y2">
-        <v>0.1157002184227059</v>
+        <v>0.1499194247171781</v>
       </c>
       <c r="Z2">
-        <v>-13.04635761589405</v>
+        <v>0.4392145940676785</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02629953856043283</v>
+        <v>0.05353218582472286</v>
       </c>
       <c r="AC2">
-        <v>-0.03097104291790766</v>
+        <v>-0.05353218582472286</v>
       </c>
       <c r="AD2">
-        <v>9.741000000000001</v>
+        <v>12.487</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9.741000000000001</v>
+        <v>12.487</v>
       </c>
       <c r="AG2">
-        <v>-83.441</v>
+        <v>-92.295</v>
       </c>
       <c r="AH2">
-        <v>0.1253006778919747</v>
+        <v>0.1599113808956677</v>
       </c>
       <c r="AI2">
-        <v>0.1742544856084865</v>
+        <v>0.2323292462835135</v>
       </c>
       <c r="AJ2">
-        <v>5.403859853636422</v>
+        <v>3.457389024161827</v>
       </c>
       <c r="AK2">
-        <v>2.23816421233336</v>
+        <v>1.808464779073185</v>
       </c>
       <c r="AL2">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-0.04500000000000001</v>
+        <v>-0.194</v>
       </c>
       <c r="AN2">
-        <v>2.459848484848485</v>
+        <v>3.106218905472637</v>
       </c>
       <c r="AO2">
-        <v>744</v>
+        <v>3810</v>
       </c>
       <c r="AP2">
-        <v>-21.0709595959596</v>
+        <v>-22.9589552238806</v>
       </c>
       <c r="AQ2">
-        <v>-82.66666666666666</v>
+        <v>-19.63917525773196</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sofia Commerce Pawn Brokerage AD (BUL:SCOM)</t>
+          <t>Bulgarian Stock Exchange AD (BUL:BSE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,109 +722,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.04769999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="E3">
-        <v>0.157</v>
+        <v>0.904</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.4354285714285714</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.3878844787644788</v>
       </c>
       <c r="K3">
-        <v>0.901</v>
+        <v>3.29</v>
       </c>
       <c r="L3">
-        <v>0.2495844875346261</v>
+        <v>0.376</v>
       </c>
       <c r="M3">
-        <v>0.9359999999999999</v>
+        <v>3.59</v>
       </c>
       <c r="N3">
-        <v>0.08830188679245282</v>
+        <v>0.113968253968254</v>
       </c>
       <c r="O3">
-        <v>1.038845726970033</v>
+        <v>1.091185410334346</v>
       </c>
       <c r="P3">
-        <v>0.619</v>
+        <v>3.59</v>
       </c>
       <c r="Q3">
-        <v>0.05839622641509434</v>
+        <v>0.113968253968254</v>
       </c>
       <c r="R3">
-        <v>0.6870144284128745</v>
+        <v>1.091185410334346</v>
       </c>
       <c r="S3">
-        <v>0.3169999999999999</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.3386752136752136</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.302</v>
+        <v>97</v>
       </c>
       <c r="V3">
-        <v>0.02849056603773585</v>
+        <v>3.07936507936508</v>
       </c>
       <c r="W3">
-        <v>0.1418897637795276</v>
+        <v>0.2030864197530864</v>
       </c>
       <c r="X3">
-        <v>0.02618954535682164</v>
+        <v>0.05250032266025442</v>
       </c>
       <c r="Y3">
-        <v>0.1157002184227059</v>
-      </c>
-      <c r="Z3">
-        <v>0.7412731006160164</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+        <v>0.150586097092832</v>
       </c>
       <c r="AB3">
-        <v>0.02629953856043283</v>
-      </c>
-      <c r="AC3">
-        <v>-0.02629953856043283</v>
+        <v>0.05250713588910733</v>
       </c>
       <c r="AD3">
-        <v>0.168</v>
+        <v>0.028</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.168</v>
+        <v>0.028</v>
       </c>
       <c r="AG3">
-        <v>-0.134</v>
+        <v>-96.97199999999999</v>
       </c>
       <c r="AH3">
-        <v>0.01560178306092125</v>
+        <v>0.0008880994671403197</v>
       </c>
       <c r="AI3">
-        <v>0.02834008097165992</v>
+        <v>0.00203962703962704</v>
       </c>
       <c r="AJ3">
-        <v>-0.01280336327154596</v>
+        <v>1.481121700879765</v>
       </c>
       <c r="AK3">
-        <v>-0.02381798791325986</v>
+        <v>1.164521087520415</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.177</v>
+      </c>
+      <c r="AN3">
+        <v>0.006965174129353235</v>
+      </c>
+      <c r="AO3">
+        <v>3810</v>
+      </c>
+      <c r="AP3">
+        <v>-24.12238805970149</v>
+      </c>
+      <c r="AQ3">
+        <v>-21.52542372881356</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ELANA Agrocredit AD (BUL:EAC)</t>
+          <t>Sofia Commerce Pawn Brokerage AD (BUL:SCOM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +847,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.308</v>
+        <v>0.0697</v>
       </c>
       <c r="E4">
-        <v>0.101</v>
+        <v>0.185</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,94 +865,88 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="L4">
-        <v>0.3065693430656934</v>
+        <v>0.3840206185567011</v>
       </c>
       <c r="M4">
-        <v>1.7808</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07675862068965517</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>1.06</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>1.5288</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.06589655172413793</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.91</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.252</v>
-      </c>
-      <c r="T4">
-        <v>0.1415094339622641</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>4.18</v>
+        <v>0.182</v>
       </c>
       <c r="V4">
-        <v>0.1801724137931034</v>
+        <v>0.01318840579710145</v>
       </c>
       <c r="W4">
-        <v>0.06640316205533596</v>
+        <v>0.2641843971631206</v>
       </c>
       <c r="X4">
-        <v>0.0300460249478573</v>
+        <v>0.0531669950359083</v>
       </c>
       <c r="Y4">
-        <v>0.03635713710747866</v>
+        <v>0.2110174021272123</v>
       </c>
       <c r="Z4">
-        <v>0.165159734779988</v>
+        <v>0.6897777777777777</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03097104291790766</v>
+        <v>0.05353218582472286</v>
       </c>
       <c r="AC4">
-        <v>-0.03097104291790766</v>
+        <v>-0.05353218582472286</v>
       </c>
       <c r="AD4">
-        <v>9.460000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9.460000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="AG4">
-        <v>5.280000000000001</v>
+        <v>0.577</v>
       </c>
       <c r="AH4">
-        <v>0.2896509491733008</v>
+        <v>0.05213270142180094</v>
       </c>
       <c r="AI4">
-        <v>0.2745211839814278</v>
+        <v>0.1051392159578889</v>
       </c>
       <c r="AJ4">
-        <v>0.1853932584269663</v>
+        <v>0.04013354663698963</v>
       </c>
       <c r="AK4">
-        <v>0.1743725231175694</v>
+        <v>0.08199516839562312</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.012</v>
-      </c>
-      <c r="AQ4">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bulgarian Stock Exchange AD (BUL:BSE)</t>
+          <t>ELANA Agrocredit AD (BUL:EAC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,118 +966,109 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.57</v>
+        <v>0.129</v>
+      </c>
+      <c r="E5">
+        <v>0.0424</v>
       </c>
       <c r="G5">
-        <v>0.3854166666666666</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.3854166666666666</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.4305555555555555</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.3807974201114043</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>1.24</v>
       </c>
       <c r="L5">
-        <v>0.3877314814814815</v>
+        <v>0.3949044585987261</v>
       </c>
       <c r="M5">
-        <v>0.901</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02634502923976608</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.268955223880597</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.115</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.003362573099415205</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.03432835820895522</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>0.786</v>
-      </c>
-      <c r="T5">
-        <v>0.8723640399556049</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>88.7</v>
+        <v>7.6</v>
       </c>
       <c r="V5">
-        <v>2.593567251461988</v>
+        <v>0.374384236453202</v>
       </c>
       <c r="W5">
-        <v>0.2723577235772358</v>
+        <v>0.0496</v>
       </c>
       <c r="X5">
-        <v>0.02606610005628785</v>
+        <v>0.05959031098351093</v>
       </c>
       <c r="Y5">
-        <v>0.2462916235209479</v>
+        <v>-0.009990310983510928</v>
       </c>
       <c r="Z5">
-        <v>-0.2192392600674973</v>
+        <v>0.1036988110964333</v>
       </c>
       <c r="AA5">
-        <v>-0.08348574462083619</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02608972386953234</v>
+        <v>0.05980299773888034</v>
       </c>
       <c r="AC5">
-        <v>-0.1095754684903685</v>
+        <v>-0.05980299773888034</v>
       </c>
       <c r="AD5">
-        <v>0.113</v>
+        <v>11.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.113</v>
+        <v>11.7</v>
       </c>
       <c r="AG5">
-        <v>-88.587</v>
+        <v>4.1</v>
       </c>
       <c r="AH5">
-        <v>0.00329321248506397</v>
+        <v>0.365625</v>
       </c>
       <c r="AI5">
-        <v>0.007284213240507961</v>
+        <v>0.3567073170731707</v>
       </c>
       <c r="AJ5">
-        <v>1.628826741684594</v>
+        <v>0.1680327868852459</v>
       </c>
       <c r="AK5">
-        <v>1.21041988331261</v>
+        <v>0.1626984126984127</v>
       </c>
       <c r="AL5">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.033</v>
-      </c>
-      <c r="AN5">
-        <v>0.02853535353535354</v>
-      </c>
-      <c r="AO5">
-        <v>744</v>
-      </c>
-      <c r="AP5">
-        <v>-22.37045454545455</v>
+        <v>-0.017</v>
       </c>
       <c r="AQ5">
-        <v>-112.7272727272727</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.129</v>
+        <v>0.1995</v>
       </c>
       <c r="E2">
-        <v>0.185</v>
+        <v>0.267</v>
       </c>
       <c r="G2">
-        <v>0.2853519340519975</v>
+        <v>0.05599268069533395</v>
       </c>
       <c r="H2">
-        <v>0.2853519340519975</v>
+        <v>0.05599268069533395</v>
       </c>
       <c r="I2">
-        <v>0.2415979708306912</v>
+        <v>0.1685269899359561</v>
       </c>
       <c r="J2">
-        <v>0.2165040893320149</v>
+        <v>0.1557959892502619</v>
       </c>
       <c r="K2">
-        <v>6.02</v>
+        <v>64.33</v>
       </c>
       <c r="L2">
-        <v>0.3817374762206722</v>
+        <v>1.177127172918573</v>
       </c>
       <c r="M2">
-        <v>3.59</v>
+        <v>16.197</v>
       </c>
       <c r="N2">
-        <v>0.05472560975609756</v>
+        <v>0.06468450479233226</v>
       </c>
       <c r="O2">
-        <v>0.5963455149501661</v>
+        <v>0.2517798849681331</v>
       </c>
       <c r="P2">
-        <v>3.59</v>
+        <v>16.197</v>
       </c>
       <c r="Q2">
-        <v>0.05472560975609756</v>
+        <v>0.06468450479233226</v>
       </c>
       <c r="R2">
-        <v>0.5963455149501661</v>
+        <v>0.2517798849681331</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>104.782</v>
+        <v>141.148</v>
       </c>
       <c r="V2">
-        <v>1.597286585365854</v>
+        <v>0.5636900958466453</v>
       </c>
       <c r="W2">
-        <v>0.2030864197530864</v>
+        <v>0.3372262773722628</v>
       </c>
       <c r="X2">
-        <v>0.0531669950359083</v>
+        <v>0.0565835146613064</v>
       </c>
       <c r="Y2">
-        <v>0.1499194247171781</v>
+        <v>0.2806427627109564</v>
       </c>
       <c r="Z2">
-        <v>0.4392145940676785</v>
+        <v>0.3590693762771109</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05353218582472286</v>
+        <v>0.05655656687714232</v>
       </c>
       <c r="AC2">
-        <v>-0.05353218582472286</v>
+        <v>-0.05655656687714232</v>
       </c>
       <c r="AD2">
-        <v>12.487</v>
+        <v>20.376</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12.487</v>
+        <v>20.376</v>
       </c>
       <c r="AG2">
-        <v>-92.295</v>
+        <v>-120.772</v>
       </c>
       <c r="AH2">
-        <v>0.1599113808956677</v>
+        <v>0.07525039146748604</v>
       </c>
       <c r="AI2">
-        <v>0.2323292462835135</v>
+        <v>0.08107075786994303</v>
       </c>
       <c r="AJ2">
-        <v>3.457389024161827</v>
+        <v>-0.9316814268522231</v>
       </c>
       <c r="AK2">
-        <v>1.808464779073185</v>
+        <v>-1.096054016771336</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="AM2">
-        <v>-0.194</v>
+        <v>-3.296</v>
       </c>
       <c r="AN2">
-        <v>3.106218905472637</v>
+        <v>7.897674418604652</v>
       </c>
       <c r="AO2">
-        <v>3810</v>
+        <v>657.8571428571429</v>
       </c>
       <c r="AP2">
-        <v>-22.9589552238806</v>
+        <v>-46.81085271317829</v>
       </c>
       <c r="AQ2">
-        <v>-19.63917525773196</v>
+        <v>-2.794296116504854</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.502</v>
+        <v>0.223</v>
       </c>
       <c r="E3">
-        <v>0.904</v>
+        <v>0.207</v>
       </c>
       <c r="G3">
-        <v>0.5142857142857142</v>
+        <v>0.3234672304439746</v>
       </c>
       <c r="H3">
-        <v>0.5142857142857142</v>
+        <v>0.3234672304439746</v>
       </c>
       <c r="I3">
-        <v>0.4354285714285714</v>
+        <v>0.2463002114164905</v>
       </c>
       <c r="J3">
-        <v>0.3878844787644788</v>
+        <v>0.2197207098369889</v>
       </c>
       <c r="K3">
-        <v>3.29</v>
+        <v>4.62</v>
       </c>
       <c r="L3">
-        <v>0.376</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="M3">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N3">
-        <v>0.113968253968254</v>
+        <v>0.0756880733944954</v>
       </c>
       <c r="O3">
-        <v>1.091185410334346</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="P3">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>0.113968253968254</v>
+        <v>0.0756880733944954</v>
       </c>
       <c r="R3">
-        <v>1.091185410334346</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,64 +770,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>97</v>
+        <v>120.4</v>
       </c>
       <c r="V3">
-        <v>3.07936507936508</v>
+        <v>2.761467889908257</v>
       </c>
       <c r="W3">
-        <v>0.2030864197530864</v>
+        <v>0.3372262773722628</v>
       </c>
       <c r="X3">
-        <v>0.05250032266025442</v>
+        <v>0.05546274669149931</v>
       </c>
       <c r="Y3">
-        <v>0.150586097092832</v>
+        <v>0.2817635306807635</v>
       </c>
       <c r="AB3">
-        <v>0.05250713588910733</v>
+        <v>0.05548880958926024</v>
       </c>
       <c r="AD3">
-        <v>0.028</v>
+        <v>0.136</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.028</v>
+        <v>0.136</v>
       </c>
       <c r="AG3">
-        <v>-96.97199999999999</v>
+        <v>-120.264</v>
       </c>
       <c r="AH3">
-        <v>0.0008880994671403197</v>
+        <v>0.00310956648984818</v>
       </c>
       <c r="AI3">
-        <v>0.00203962703962704</v>
+        <v>0.008534136546184739</v>
       </c>
       <c r="AJ3">
-        <v>1.481121700879765</v>
+        <v>1.568715433580298</v>
       </c>
       <c r="AK3">
-        <v>1.164521087520415</v>
+        <v>1.151248276918364</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>-0.177</v>
+        <v>-3.307</v>
       </c>
       <c r="AN3">
-        <v>0.006965174129353235</v>
+        <v>0.05271317829457364</v>
       </c>
       <c r="AO3">
-        <v>3810</v>
+        <v>776.6666666666666</v>
       </c>
       <c r="AP3">
-        <v>-24.12238805970149</v>
+        <v>-46.6139534883721</v>
       </c>
       <c r="AQ3">
-        <v>-21.52542372881356</v>
+        <v>-0.7045660719685516</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sofia Commerce Pawn Brokerage AD (BUL:SCOM)</t>
+          <t>Advance Terrafund REIT (BUL:ATER)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0697</v>
+        <v>0.382</v>
       </c>
       <c r="E4">
-        <v>0.185</v>
+        <v>0.327</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,94 +859,103 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.2301003344481606</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.2301003344481606</v>
       </c>
       <c r="K4">
-        <v>1.49</v>
+        <v>55</v>
       </c>
       <c r="L4">
-        <v>0.3840206185567011</v>
+        <v>1.839464882943144</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>10.7</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06729559748427673</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1945454545454545</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>10.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06729559748427673</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1945454545454545</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.182</v>
+        <v>15.3</v>
       </c>
       <c r="V4">
-        <v>0.01318840579710145</v>
+        <v>0.09622641509433963</v>
       </c>
       <c r="W4">
-        <v>0.2641843971631206</v>
+        <v>0.4467912266450041</v>
       </c>
       <c r="X4">
-        <v>0.0531669950359083</v>
+        <v>0.05541609965942788</v>
       </c>
       <c r="Y4">
-        <v>0.2110174021272123</v>
+        <v>0.3913751269855762</v>
       </c>
       <c r="Z4">
-        <v>0.6897777777777777</v>
+        <v>0.2639244416982964</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.06072910230382205</v>
       </c>
       <c r="AB4">
-        <v>0.05353218582472286</v>
+        <v>0.05541609965942788</v>
       </c>
       <c r="AC4">
-        <v>-0.05353218582472286</v>
+        <v>0.005313002644394167</v>
       </c>
       <c r="AD4">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.759</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.577</v>
+        <v>-15.3</v>
       </c>
       <c r="AH4">
-        <v>0.05213270142180094</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.1051392159578889</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.04013354663698963</v>
+        <v>-0.1064718162839249</v>
       </c>
       <c r="AK4">
-        <v>0.08199516839562312</v>
+        <v>-0.09473684210526316</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.003</v>
+      </c>
+      <c r="AO4">
+        <v>2293.333333333333</v>
+      </c>
+      <c r="AQ4">
+        <v>2293.333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -957,118 +966,359 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Sofia Commerce-Pawn Brokerage AD (BUL:SCOM)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.102</v>
+      </c>
+      <c r="E5">
+        <v>0.36</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>2.14</v>
+      </c>
+      <c r="L5">
+        <v>0.4015009380863039</v>
+      </c>
+      <c r="M5">
+        <v>0.741</v>
+      </c>
+      <c r="N5">
+        <v>0.04780645161290323</v>
+      </c>
+      <c r="O5">
+        <v>0.3462616822429906</v>
+      </c>
+      <c r="P5">
+        <v>0.741</v>
+      </c>
+      <c r="Q5">
+        <v>0.04780645161290323</v>
+      </c>
+      <c r="R5">
+        <v>0.3462616822429906</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1.09</v>
+      </c>
+      <c r="V5">
+        <v>0.0703225806451613</v>
+      </c>
+      <c r="W5">
+        <v>0.3312693498452012</v>
+      </c>
+      <c r="X5">
+        <v>0.0565835146613064</v>
+      </c>
+      <c r="Y5">
+        <v>0.2746858351838948</v>
+      </c>
+      <c r="Z5">
+        <v>0.757425039079153</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05655656687714232</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05655656687714232</v>
+      </c>
+      <c r="AD5">
+        <v>1.21</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.21</v>
+      </c>
+      <c r="AG5">
+        <v>0.1199999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.07241172950329143</v>
+      </c>
+      <c r="AI5">
+        <v>0.1069849690539346</v>
+      </c>
+      <c r="AJ5">
+        <v>0.007682458386683732</v>
+      </c>
+      <c r="AK5">
+        <v>0.01174168297455968</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ITF Group AD (BUL:ITF)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0.1890359168241966</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.488</v>
+      </c>
+      <c r="V6">
+        <v>0.04477064220183486</v>
+      </c>
+      <c r="W6">
+        <v>0.4926108374384237</v>
+      </c>
+      <c r="X6">
+        <v>0.06039635631881788</v>
+      </c>
+      <c r="Y6">
+        <v>0.4322144811196058</v>
+      </c>
+      <c r="Z6">
+        <v>0.7928657074340528</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06125774099624993</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06125774099624993</v>
+      </c>
+      <c r="AD6">
+        <v>3.63</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>3.63</v>
+      </c>
+      <c r="AG6">
+        <v>3.142</v>
+      </c>
+      <c r="AH6">
+        <v>0.2498279421885753</v>
+      </c>
+      <c r="AI6">
+        <v>0.4037819799777531</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2237572995299815</v>
+      </c>
+      <c r="AK6">
+        <v>0.3695601035050576</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>ELANA Agrocredit AD (BUL:EAC)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.129</v>
-      </c>
-      <c r="E5">
-        <v>0.0424</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1.24</v>
-      </c>
-      <c r="L5">
-        <v>0.3949044585987261</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>7.6</v>
-      </c>
-      <c r="V5">
-        <v>0.374384236453202</v>
-      </c>
-      <c r="W5">
-        <v>0.0496</v>
-      </c>
-      <c r="X5">
-        <v>0.05959031098351093</v>
-      </c>
-      <c r="Y5">
-        <v>-0.009990310983510928</v>
-      </c>
-      <c r="Z5">
-        <v>0.1036988110964333</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05980299773888034</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05980299773888034</v>
-      </c>
-      <c r="AD5">
-        <v>11.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>11.7</v>
-      </c>
-      <c r="AG5">
-        <v>4.1</v>
-      </c>
-      <c r="AH5">
-        <v>0.365625</v>
-      </c>
-      <c r="AI5">
-        <v>0.3567073170731707</v>
-      </c>
-      <c r="AJ5">
-        <v>0.1680327868852459</v>
-      </c>
-      <c r="AK5">
-        <v>0.1626984126984127</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>-0.017</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+      <c r="D7">
+        <v>0.176</v>
+      </c>
+      <c r="E7">
+        <v>0.0703</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1.57</v>
+      </c>
+      <c r="L7">
+        <v>0.3361884368308352</v>
+      </c>
+      <c r="M7">
+        <v>1.456</v>
+      </c>
+      <c r="N7">
+        <v>0.06803738317757009</v>
+      </c>
+      <c r="O7">
+        <v>0.927388535031847</v>
+      </c>
+      <c r="P7">
+        <v>1.456</v>
+      </c>
+      <c r="Q7">
+        <v>0.06803738317757009</v>
+      </c>
+      <c r="R7">
+        <v>0.927388535031847</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>3.87</v>
+      </c>
+      <c r="V7">
+        <v>0.1808411214953271</v>
+      </c>
+      <c r="W7">
+        <v>0.07440758293838862</v>
+      </c>
+      <c r="X7">
+        <v>0.06617774177530034</v>
+      </c>
+      <c r="Y7">
+        <v>0.008229841163088281</v>
+      </c>
+      <c r="Z7">
+        <v>0.1853174603174604</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06520123372346233</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06520123372346233</v>
+      </c>
+      <c r="AD7">
+        <v>15.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>15.4</v>
+      </c>
+      <c r="AG7">
+        <v>11.53</v>
+      </c>
+      <c r="AH7">
+        <v>0.4184782608695652</v>
+      </c>
+      <c r="AI7">
+        <v>0.4020887728459531</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3501366535074401</v>
+      </c>
+      <c r="AK7">
+        <v>0.33488237002614</v>
+      </c>
+      <c r="AL7">
+        <v>0.008</v>
+      </c>
+      <c r="AM7">
+        <v>0.008</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
